--- a/similarity_matrix.xlsx
+++ b/similarity_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH34"/>
+  <dimension ref="A1:AK33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,164 +441,182 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>activity1 (have a hip fracture care pathway that clearly specifies perioperative patient goals by day of stay (Role: hospital; Objects: hip fracture care pathway))</t>
+          <t>activity1 (Risk stratification
+(e.g., EHMRG))</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>parallelgateway1 (Parallel Gateway)</t>
+          <t>parallelgateway1_modified (Parallel Gateway)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>activity2 (Seen by physician)</t>
+          <t>activity_bloodwork1 (Serum creatinine and electrolyte levels)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>activity3 (Consultation with orthopaedic surgeon)</t>
+          <t>activity_bloodwork_interpret1 (interpret bloodwork results (Role: healthcare expert; Objects: bloodwork results))</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>parallelgateway1Join (Parallel Merge)</t>
+          <t>activity5 (Electrocardiogram)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>inclusivegateway1 (Inclusive Gateway)</t>
+          <t>activity_ecg_interpret1 (interpret electrocardiogram (Role: healthcare expert; Objects: electrocardiogram results))</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>activity4 (Consultation with anesthesiologists / internist)</t>
+          <t>activity6_mod (Chest x-ray)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>activity5 (be made aware of the patient and provide consultation as needed (Role: internist; Objects: patient))</t>
+          <t>activity_cxr_interpret1_mod (interpret chest x-ray (if performed) (Role: healthcare expert; Objects: chest x-ray results))</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>inclusivegateway1Join (Inclusive Merge)</t>
+          <t>exclusivegateway1 (Exclusive Gateway)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>parallelgateway_new1_mod (Parallel Gateway)</t>
+          <t>activity7 (Echocardiogram)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>activity6a_bloodwork (Issue appropriate blood work)</t>
+          <t>activity_echo_interpret1 (interpret echocardiogram (Role: healthcare expert; Objects: echocardiogram results))</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>activity6b_interpret_bloodwork (interpret blood work results and document findings (Role: healthcare expert; Objects: blood work results))</t>
+          <t>activity8 (Echocardiogram)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>activity6a_xray (Perform x-ray)</t>
+          <t>activity_recent_echo_interpret1 (interpret recent echocardiogram (Role: healthcare expert; Objects: recent echocardiogram findings))</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>activity6c_interpret_xray (interpret X-ray results and document findings (Role: healthcare expert; Objects: X-ray results))</t>
+          <t>exclusivegateway1Join (Exclusive Merge)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>activity6_comp (Assess reason for fall)</t>
+          <t>activity9 (Monitor heart rate, blood pressure, oxygen saturation until stabilized)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>parallelgateway_new1_modJoin (Parallel Merge)</t>
+          <t>parallelgateway1_modifiedJoin (Parallel Merge)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>parallelgateway2 (Parallel Gateway)</t>
+          <t>activity10_1 (Risk stratification
+(e.g., EHMRG))</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>activity7 (Perform medication reconciliation within the ED)</t>
+          <t>activity10_2 (assist with clinical decision-making (Role: clinicians))</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>parallelgateway4 (Parallel Gateway)</t>
+          <t>activity10_3 (Risk stratification
+(e.g., EHMRG))</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>activity8.1 (Manage patients' hydration, pain, risk of delirium and risk of pressure sores within the ED)</t>
+          <t>exclusivegateway2 (Exclusive Gateway)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>activity8.2 (Assess pain)</t>
+          <t>exclusivegateway3 (Exclusive Gateway)</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>activity8.3 (take steps within the ED to manage risk of delirium (Role: clinical staff; Objects: risk of delirium))</t>
+          <t>activity11 (Treat in ED)</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>activity8.4 (Assess pressure sore risk)</t>
+          <t>activity12 (Discharge home)</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>parallelgateway4Join (Parallel Merge)</t>
+          <t>exclusivegateway3Join (Exclusive Merge)</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>parallelgateway2Join (Parallel Merge)</t>
+          <t>activity13 (Arrange follow-up (within days) with primary care)</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>exclusivegateway1 (Exclusive Gateway)</t>
+          <t>exclusivegateway4_modified (Exclusive Gateway)</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>activity9 (Medically stabilize while waiting for expeditious transfer to a surgical hospital for operation based on formal protocol)</t>
+          <t>inclusivegateway_high_intensity_actions (Inclusive Gateway)</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>activity10 (ensure surgery within 48 hours of initial presentation (Role: clinical staff; Objects: patient))</t>
+          <t>activity15 (provide noninvasive ventilation (Role: clinicians; Objects: ventilation))</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>activity12 (Admit patient)</t>
+          <t>activity16 (invasive ventilation)</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>activity13 (have patient proceed under hip fracture care pathway (Role: hospital; Objects: patient))</t>
+          <t>activity17 (Admit to ICU (high nurse-to-patient staffing))</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>exclusivegateway1Join (Exclusive Merge)</t>
+          <t>inclusivegateway_high_intensity_actionsJoin (Inclusive Merge)</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>activity14 (Admit to inpatient care (normal nurse-to-patient staffing))</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>exclusivegateway4_modifiedJoin (Exclusive Merge)</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>exclusivegateway2Join (Exclusive Merge)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>T_OrthoConsult (Consultation with orthopaedic surgeon)</t>
+          <t>_84936A37-661C-435C-A4A9-BA815D74BE3F (Exclusive Merge)</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -608,49 +626,49 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1456953642384106</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1891891891891891</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6470588235294117</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.5106382978723405</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.1919191919191919</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.2432432432432432</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.180952380952381</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.1081081081081081</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.1894736842105263</v>
-      </c>
       <c r="R2" t="n">
-        <v>0.1621621621621622</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -659,52 +677,61 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2127659574468085</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2307692307692307</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1621621621621622</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1683168316831684</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1621621621621622</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1916666666666667</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.2105263157894737</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1891891891891891</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.1954022988505747</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>T_MedicationReconciliation (Perform medication reconciliation within the ED)</t>
+          <t>_BBB29E42-2F99-4B33-BE9F-FB16AE2BA1FC (Discharge home)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -714,103 +741,112 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1721854304635762</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.148936170212766</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2127659574468085</v>
+        <v>0.09876543209876543</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.1123595505617978</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1702127659574468</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2626262626262627</v>
+        <v>0.08695652173913049</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1914893617021277</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2127659574468085</v>
+        <v>0.1020408163265306</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1914893617021277</v>
+        <v>0.1285714285714286</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="U3" t="n">
+        <v>0.1454545454545455</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.3186813186813187</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.1063829787234043</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.198019801980198</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.1063829787234043</v>
-      </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.1224489795918368</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2421052631578947</v>
+        <v>0.09722222222222221</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1914893617021277</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1954022988505747</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>T_EDManagement (Manage patients' hydration, pain, risk of delirium and risk of pressure sores within the ED)</t>
+          <t>_BEB390D8-2407-46FF-BDDE-66FE45EC9373 (Treat in ED)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -820,103 +856,112 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2450331125827815</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1318681318681318</v>
+        <v>0.1794871794871795</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2307692307692307</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.0786516853932584</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2197802197802198</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2525252525252525</v>
+        <v>0.06521739130434778</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.08433734939759041</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07692307692307687</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1473684210526316</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.09090909090909094</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
         <v>0.1428571428571429</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.3186813186813187</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.08791208791208793</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.306930693069307</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.2197802197802198</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1894736842105263</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09890109890109888</v>
+        <v>0.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2197802197802198</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>XG_NonSurgicalHosp (presenting to non-surgical hospital?)</t>
+          <t>_696801DA-21DC-44A9-B388-73A9A117E8C0 (Check responsiveness to Diuresis)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -926,61 +971,61 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.06060606060606055</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.1975308641975309</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.1797752808988764</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.21875</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.1630434782608695</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.15625</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.1807228915662651</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.15625</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.1632653061224489</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.06060606060606055</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.06060606060606055</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -989,40 +1034,49 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>0.2040816326530612</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1111111111111112</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>0.1944444444444444</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.1111111111111112</v>
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>T_NS_Stabilize (Medically stabilize while waiting for expeditious transfer to a surgical hospital for operation based on formal protocol)</t>
+          <t>SE_Start ()</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1032,16 +1086,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2582781456953642</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09999999999999998</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1916666666666667</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1050,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2166666666666667</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1062,19 +1116,19 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2166666666666667</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06666666666666665</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2166666666666667</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1083,22 +1137,22 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2333333333333333</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.08333333333333337</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2416666666666667</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1110,25 +1164,34 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.2333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.09166666666666667</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.2416666666666667</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Gateway_1kybgw7 (Parallel Merge)</t>
+          <t>PG_DiagnosticsSplit (Parallel Gateway)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1141,58 +1204,58 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>0.625</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
       <c r="T7" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1207,10 +1270,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1228,13 +1291,22 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Activity_1t89ztw (Admit patient)</t>
+          <t>PG_DiagnosticsJoin (Parallel Merge)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1244,16 +1316,16 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06622516556291391</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1764705882352942</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1891891891891891</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1262,10 +1334,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1702127659574468</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1111111111111112</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1274,43 +1346,43 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1428571428571429</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08571428571428574</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.09473684210526312</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1363636363636364</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1914893617021277</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.09890109890109888</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3846153846153846</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.07920792079207917</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1322,25 +1394,34 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.09166666666666667</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.1052631578947368</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.1264367816091954</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Gateway_0gdnuu0 (Exclusive Merge)</t>
+          <t>T_Labs (Serum creatinine and electrolyte levels)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1350,61 +1431,61 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.1794871794871795</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.2471910112359551</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.1282051282051282</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.2282608695652174</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.1025641025641025</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.2409638554216867</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.1025641025641025</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.2040816326530612</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.1794871794871795</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1794871794871795</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1413,40 +1494,49 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.1794871794871795</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>0.1632653061224489</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.6470588235294117</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>0.2083333333333334</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.2051282051282052</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Activity_1a31rg3 (Consultation with anesthesiologists / internist)</t>
+          <t>T_Troponin (Troponin measurements)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1456,103 +1546,112 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1721854304635762</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1702127659574468</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5106382978723405</v>
+        <v>0.1358024691358025</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.1348314606741573</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.1195652173913043</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2340425531914894</v>
+        <v>0.1445783132530121</v>
       </c>
       <c r="O10" t="n">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1326530612244898</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1571428571428571</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.1636363636363637</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.1836734693877551</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.1944444444444444</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="AG10" t="n">
         <v>0.2</v>
       </c>
-      <c r="P10" t="n">
-        <v>0.08510638297872342</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.1276595744680851</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.1702127659574468</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.2197802197802198</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.1702127659574468</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.2178217821782178</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.2127659574468085</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.2166666666666667</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.2315789473684211</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.1702127659574468</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.2298850574712644</v>
-      </c>
       <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Gateway_12io2a5 (Parallel Gateway)</t>
+          <t>T_CBC (Complete blood count)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1562,61 +1661,61 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.09090909090909094</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.2051282051282052</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.1728395061728395</v>
       </c>
       <c r="H11" t="n">
-        <v>0.625</v>
+        <v>0.15</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.1573033707865169</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.1304347826086957</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.1566265060240963</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.1224489795918368</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="S11" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>0.09090909090909094</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.1454545454545455</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0.09090909090909094</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1625,16 +1724,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.625</v>
+        <v>0.1224489795918368</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1643,22 +1742,31 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>0.1527777777777778</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.1896551724137931</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Gateway_0dmr7rz (consult needed?)</t>
+          <t>T_ECG (Electrocardiogram)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1668,61 +1776,61 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.1234567901234568</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.1797752808988764</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.2352941176470589</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.1086956521739131</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.1807228915662651</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.1632653061224489</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.1285714285714286</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.1454545454545455</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1731,40 +1839,49 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>0.1224489795918368</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1764705882352942</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>0.08333333333333337</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.1379310344827587</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Gateway_1fxeuks (Exclusive Merge)</t>
+          <t>T_CXR (Chest x-ray)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1774,61 +1891,61 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.09090909090909094</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.1282051282051282</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.2352941176470589</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.0786516853932584</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.1086956521739131</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.08433734939759041</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.09090909090909094</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.09090909090909094</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.09090909090909094</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1837,40 +1954,49 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>0.1224489795918368</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.6470588235294117</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>0.06944444444444442</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.08620689655172409</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>T_SeenByPhysician (Seen by physician)</t>
+          <t>XG_Echo (recent echocardiogram available?)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1880,16 +2006,16 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08609271523178808</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1891891891891891</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1898,31 +2024,31 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1702127659574468</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1111111111111112</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0714285714285714</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.08571428571428574</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1764705882352942</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.09473684210526312</v>
+        <v>0.125</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1363636363636364</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1931,52 +2057,61 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.148936170212766</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1318681318681318</v>
+        <v>0.125</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2352941176470589</v>
+        <v>0.125</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.09900990099009899</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.09999999999999998</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.1263157894736842</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1764705882352942</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.1494252873563219</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Gateway_1gkqhzc (admit patient?)</t>
+          <t>T_Echo (Echocardiogram)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1986,61 +2121,61 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.1025641025641025</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.0864197530864198</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.1460674157303371</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.08695652173913049</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.1566265060240963</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.1326530612244898</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.1454545454545455</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2049,40 +2184,49 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>0.1020408163265306</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.2352941176470589</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>0.06944444444444442</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>0.08888888888888891</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.06666666666666665</v>
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Gateway_02qyxwz (Exclusive Merge)</t>
+          <t>T_Monitor (Monitor heart rate, blood pressure, oxygen saturation until stabilized)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2092,61 +2236,61 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.1571428571428571</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.1285714285714286</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.1797752808988764</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.1686746987951807</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.2040816326530612</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.1571428571428571</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.1714285714285714</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1571428571428571</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2155,40 +2299,50 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>0.1285714285714286</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>0.1857142857142857</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.6470588235294117</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>0.1527777777777778</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.1857142857142857</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>0.2714285714285715</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.2571428571428571</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Event_016y4oe ()</t>
+          <t>T_RiskAssessment (Risk stratification
+(e.g., EHMRG))</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2198,61 +2352,61 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.1794871794871795</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.1234567901234568</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.1348314606741573</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.09090909090909094</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.1413043478260869</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.1224489795918368</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.1571428571428571</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.2545454545454545</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -2261,16 +2415,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>0.08163265306122447</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2279,22 +2433,31 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>0.1944444444444444</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Activity_1i7wmma (Perform x-ray)</t>
+          <t>XG_RiskGroup (risk stratification outcome?)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2304,16 +2467,16 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05960264900662249</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1764705882352942</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1081081081081081</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2322,31 +2485,31 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08510638297872342</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.07070707070707072</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>0.1428571428571429</v>
       </c>
-      <c r="O18" t="n">
-        <v>0.07619047619047614</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.1157894736842106</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.2272727272727273</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -2355,52 +2518,61 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2127659574468085</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.07692307692307687</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="X18" t="n">
-        <v>0.07692307692307687</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.06930693069306926</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.06666666666666665</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0736842105263158</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.09195402298850575</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.1428571428571429</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Event_0fk6zjq ()</t>
+          <t>T_Low_Followup (Arrange follow-up (within days) with primary care)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2410,61 +2582,61 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.08163265306122447</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.1632653061224489</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.1224489795918368</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.2134831460674157</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.1224489795918368</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.1847826086956522</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.1020408163265306</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.2168674698795181</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.1020408163265306</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.1938775510204082</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.1857142857142857</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.08163265306122447</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.1272727272727273</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.08163265306122447</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -2473,16 +2645,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>0.1224489795918368</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2491,22 +2663,31 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>0.1944444444444444</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>0.1632653061224489</v>
       </c>
       <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.1551724137931034</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Activity_01k8j17 (Assess reason for fall)</t>
+          <t>T_Avg_AdmitInpatient (Admit to inpatient care (normal nurse-to-patient staffing))</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2516,103 +2697,112 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.09933774834437081</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1621621621621622</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.1379310344827587</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1276595744680851</v>
+        <v>0.08620689655172409</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.2282608695652174</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>0.1206896551724138</v>
       </c>
       <c r="N20" t="n">
-        <v>0.25</v>
+        <v>0.2168674698795181</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1206896551724138</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.2551020408163265</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1473684210526316</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
+        <v>0.2571428571428571</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.1551724137931034</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.6551724137931034</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.1914893617021277</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.1428571428571429</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.4090909090909091</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.1485148514851485</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.1578947368421053</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0.1363636363636364</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0.1379310344827587</v>
-      </c>
-      <c r="AH20" t="n">
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Activity_10uykop (Assess fluid balance)</t>
+          <t>IG_High_Split (Inclusive Gateway)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2622,16 +2812,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.08609271523178808</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1621621621621622</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2640,10 +2830,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1702127659574468</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1111111111111112</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2652,19 +2842,19 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2142857142857143</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1238095238095238</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1368421052631579</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3636363636363636</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2673,22 +2863,22 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.148936170212766</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1208791208791209</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1386138613861386</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -2700,25 +2890,34 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.1083333333333333</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.1473684210526316</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.1149425287356322</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
+        <v>0.6470588235294117</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Activity_03uuqcf (Assess pressure sore risk)</t>
+          <t>T_High_Ventilation (noninvasive ventilation)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2728,103 +2927,112 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1059602649006622</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.16</v>
+        <v>0.2051282051282052</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1621621621621622</v>
+        <v>0.1234567901234568</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.04347826086956519</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.1348314606741573</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2127659574468085</v>
+        <v>0.1304347826086957</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.09782608695652173</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.08695652173913049</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3571428571428571</v>
+        <v>0.1445783132530121</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1619047619047619</v>
+        <v>0.08695652173913049</v>
       </c>
       <c r="P22" t="n">
+        <v>0.1326530612244898</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.1304347826086957</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.1304347826086957</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.1632653061224489</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.3194444444444444</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="AG22" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0.1684210526315789</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.1063829787234043</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.2197802197802198</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.1584158415841584</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0.1578947368421053</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.1609195402298851</v>
-      </c>
       <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.2241379310344828</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Activity_1ukkw5u (Assess hydration and nutrition)</t>
+          <t>T_High_TransferICU (Admit to ICU (high nurse-to-patient staffing))</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2834,103 +3042,112 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1125827814569537</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2432432432432432</v>
+        <v>0.1604938271604939</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.1910112359550562</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2127659574468085</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2121212121212122</v>
+        <v>0.1847826086956522</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.08888888888888891</v>
       </c>
       <c r="N23" t="n">
+        <v>0.1807228915662651</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.08888888888888891</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.2244897959183674</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.2714285714285715</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.2181818181818181</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.1632653061224489</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.1944444444444444</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0.2</v>
       </c>
-      <c r="O23" t="n">
-        <v>0.1428571428571429</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.1666666666666666</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.1473684210526316</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.2978723404255319</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0.2527472527472527</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.3333333333333334</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.1584158415841584</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.3333333333333334</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.1666666666666666</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0.1894736842105263</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0.2333333333333333</v>
-      </c>
       <c r="AG23" t="n">
-        <v>0.1609195402298851</v>
+        <v>1</v>
       </c>
       <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.6551724137931034</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Activity_1jobs1d (Assess pain)</t>
+          <t>Activity_0gxp8k2 (invasive ventilation)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2940,103 +3157,112 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.05960264900662249</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2352941176470589</v>
+        <v>0.2051282051282052</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1621621621621622</v>
+        <v>0.1234567901234568</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.1348314606741573</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1702127659574468</v>
+        <v>0.15</v>
       </c>
       <c r="K24" t="n">
-        <v>0.101010101010101</v>
+        <v>0.1086956521739131</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.1445783132530121</v>
       </c>
       <c r="O24" t="n">
-        <v>0.05714285714285716</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="P24" t="n">
-        <v>0.07692307692307687</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0736842105263158</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.1857142857142857</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1063829787234043</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="W24" t="n">
-        <v>0.08791208791208793</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1</v>
       </c>
-      <c r="Y24" t="n">
-        <v>0.06930693069306926</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.08333333333333337</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0.1052631578947368</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0.3846153846153846</v>
-      </c>
       <c r="AG24" t="n">
-        <v>0.09195402298850575</v>
+        <v>0.2</v>
       </c>
       <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Activity_0zev4nn (Assess temperature)</t>
+          <t>Gateway_0rftpko (invasive?)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -3046,16 +3272,16 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.09933774834437081</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1111111111111112</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2162162162162162</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -3064,31 +3290,31 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.148936170212766</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1111111111111112</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.2352941176470589</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1238095238095238</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1666666666666666</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1368421052631579</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4090909090909091</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -3097,52 +3323,61 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1276595744680851</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1208791208791209</v>
+        <v>0.2352941176470589</v>
       </c>
       <c r="X25" t="n">
-        <v>0.5</v>
+        <v>0.2352941176470589</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.1287128712871287</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.4399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>0.2352941176470589</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.1083333333333333</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.1157894736842106</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.2222222222222222</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.1264367816091954</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Activity_1jessoe (Assess other collateral injuries)</t>
+          <t>Gateway_0dhp7yv (Exclusive Merge)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -3152,16 +3387,16 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1324503311258278</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.15625</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2162162162162162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3170,31 +3405,31 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2553191489361702</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2222222222222222</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1714285714285714</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1875</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1894736842105263</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.34375</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -3203,52 +3438,61 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2127659574468085</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1648351648351648</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="X26" t="n">
-        <v>0.3125</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.198019801980198</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.1894736842105263</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.1875</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.1954022988505747</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Activity_01jin4d (Issue appropriate blood work)</t>
+          <t>IG_High_Join (Inclusive Merge)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -3258,16 +3502,16 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1390728476821192</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0714285714285714</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2432432432432432</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3276,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2340425531914894</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1616161616161617</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3288,73 +3532,82 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.6470588235294117</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1</v>
       </c>
-      <c r="O27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.1428571428571429</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.1368421052631579</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.1914893617021277</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0.1538461538461539</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0.1785714285714286</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0.1584158415841584</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0.3571428571428571</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0.1578947368421053</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0.1428571428571429</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.1609195402298851</v>
-      </c>
-      <c r="AH27" t="n">
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Activity_1gz36ql (Assess comorbid conditions)</t>
+          <t>Gateway_0jkjljq (Parallel Gateway)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -3364,16 +3617,16 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08609271523178808</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2692307692307693</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1891891891891891</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -3382,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1914893617021277</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1414141414141414</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3394,43 +3647,43 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1538461538461539</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1263157894736842</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3461538461538461</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0.2340425531914894</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.1318681318681318</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.3461538461538461</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1485148514851485</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.3846153846153846</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -3442,25 +3695,34 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.1473684210526316</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.2692307692307693</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.1379310344827587</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Activity_0rdxay7 (Assess current drug therapy)</t>
+          <t>Gateway_1yicscu (Parallel Merge)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3470,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1258278145695364</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1481481481481481</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1621621621621622</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -3488,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1702127659574468</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1313131313131313</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3500,43 +3762,43 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.1785714285714286</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1523809523809524</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2592592592592593</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1789473684210526</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.4074074074074074</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2127659574468085</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0.1428571428571429</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.2962962962962963</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.1386138613861386</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.4074074074074074</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -3548,25 +3810,34 @@
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.1578947368421053</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.1851851851851852</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.1609195402298851</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Activity_0uqtu4t (Assess continence)</t>
+          <t>Gateway_0xdpgkt (Exclusive Merge)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -3576,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.07947019867549665</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.05882352941176472</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1891891891891891</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -3594,31 +3865,31 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2127659574468085</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1212121212121212</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.2142857142857143</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1142857142857143</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1176470588235294</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1263157894736842</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.4090909090909091</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -3627,52 +3898,61 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2127659574468085</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.1208791208791209</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="X30" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.1089108910891089</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.1083333333333333</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.1368421052631579</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.3529411764705882</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.09195402298850575</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
         <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Activity_18rs3qq (Assess pre-fracture functional ability, mobility)</t>
+          <t>Event_09cc4l6 ()</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -3682,16 +3962,16 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1854304635761589</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1666666666666666</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1458333333333334</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -3700,10 +3980,10 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1041666666666666</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2222222222222222</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3712,19 +3992,19 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0.180952380952381</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.1458333333333334</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1894736842105263</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3333333333333334</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3733,22 +4013,22 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0.1666666666666666</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0.1978021978021978</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.2291666666666666</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.2178217821782178</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.3541666666666666</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -3760,25 +4040,34 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.1833333333333333</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.2421052631578947</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.1666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.2758620689655172</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Activity_0mqj2lu (Assess physical, functional level)</t>
+          <t>Gateway_1ka7c91 (treat in ED?)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -3788,16 +4077,16 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1258278145695364</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2424242424242424</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1351351351351351</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3806,31 +4095,31 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.148936170212766</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1616161616161617</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2121212121212122</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1428571428571429</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1212121212121212</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.1684210526315789</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3939393939393939</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -3839,52 +4128,61 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0.2553191489361702</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.1758241758241759</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="X32" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.1683168316831684</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.3636363636363636</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.1666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.2121212121212122</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.1609195402298851</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.1333333333333333</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Activity_07pqefl (Assess mental state based on pre-morbid functioning level)</t>
+          <t>Gateway_0h1qfus (Exclusive Merge)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -3894,16 +4192,16 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1854304635761589</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1929824561403509</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2280701754385965</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3912,31 +4210,31 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1929824561403509</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2323232323232324</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0.2280701754385965</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.08771929824561409</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2105263157894737</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0.3333333333333334</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -3945,152 +4243,55 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2456140350877193</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2527472527472527</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1754385964912281</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.2574257425742574</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2807017543859649</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.2166666666666667</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.2210526315789474</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.1578947368421053</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.2068965517241379</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Activity_0gog65i (Assess social circumstances)</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.1125827814569537</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.1891891891891891</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.2127659574468085</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.1313131313131313</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.1428571428571429</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.1428571428571429</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.1851851851851852</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.1578947368421053</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.3703703703703703</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.1914893617021277</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.1648351648351648</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.3703703703703703</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0.1683168316831684</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0.2962962962962963</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0.1894736842105263</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0.1851851851851852</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0.1609195402298851</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
